--- a/report/Cycle-by-Cycle.xlsx
+++ b/report/Cycle-by-Cycle.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D3B257-E5F5-4FF0-BD79-96FF4599E984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B8789-74DE-4E26-8180-200C284B8956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
     <sheet name="工作表2" sheetId="4" r:id="rId2"/>
+    <sheet name="工作表3" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="119">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -499,6 +500,18 @@
   </si>
   <si>
     <t>TEMP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -679,6 +692,12 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,15 +705,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -712,13 +722,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1036,45 +1049,45 @@
     <row r="1" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="9" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="18" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="12" t="s">
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="14"/>
-      <c r="X2" s="9" t="s">
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="11"/>
-      <c r="AA2" s="9" t="s">
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="11"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="13"/>
     </row>
     <row r="3" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -2176,60 +2189,60 @@
     <row r="1" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="9" t="s">
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="18" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="12" t="s">
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="9" t="s">
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
-      <c r="AA2" s="10"/>
-      <c r="AB2" s="10"/>
-      <c r="AC2" s="10"/>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="9" t="s">
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="12"/>
+      <c r="AC2" s="12"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="10"/>
-      <c r="AG2" s="10"/>
-      <c r="AH2" s="10"/>
-      <c r="AI2" s="10"/>
-      <c r="AJ2" s="10"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="10"/>
-      <c r="AM2" s="11"/>
-      <c r="AN2" s="15" t="s">
+      <c r="AF2" s="12"/>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="12"/>
+      <c r="AL2" s="12"/>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="16"/>
-      <c r="AP2" s="17"/>
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="16"/>
     </row>
     <row r="3" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -2357,7 +2370,7 @@
       </c>
     </row>
     <row r="4" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22">
+      <c r="B4" s="10">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -2391,31 +2404,31 @@
       <c r="S4" s="6"/>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
-      <c r="V4" s="21" t="s">
+      <c r="V4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W4" s="21">
-        <v>0</v>
-      </c>
-      <c r="X4" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="21" t="s">
+      <c r="W4" s="9">
+        <v>0</v>
+      </c>
+      <c r="X4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA4" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="21" t="s">
+      <c r="AA4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE4" s="4"/>
@@ -2432,7 +2445,7 @@
       <c r="AP4" s="3"/>
     </row>
     <row r="5" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="22">
+      <c r="B5" s="10">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -2470,31 +2483,31 @@
       <c r="S5" s="6"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
-      <c r="V5" s="21" t="s">
+      <c r="V5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W5" s="21">
-        <v>0</v>
-      </c>
-      <c r="X5" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="21" t="s">
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="21" t="s">
+      <c r="AA5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE5" s="4"/>
@@ -2511,7 +2524,7 @@
       <c r="AP5" s="3"/>
     </row>
     <row r="6" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="22">
+      <c r="B6" s="10">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -2553,31 +2566,31 @@
       <c r="S6" s="6"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
-      <c r="V6" s="21" t="s">
+      <c r="V6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W6" s="21">
-        <v>0</v>
-      </c>
-      <c r="X6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="21" t="s">
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="21" t="s">
+      <c r="AA6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE6" s="4"/>
@@ -2640,31 +2653,31 @@
       <c r="S7" s="6"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
-      <c r="V7" s="21" t="s">
+      <c r="V7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W7" s="21">
-        <v>0</v>
-      </c>
-      <c r="X7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="21" t="s">
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="21" t="s">
+      <c r="AA7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE7" s="4"/>
@@ -2735,31 +2748,31 @@
       <c r="S8" s="6"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
-      <c r="V8" s="21" t="s">
+      <c r="V8" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W8" s="21">
-        <v>0</v>
-      </c>
-      <c r="X8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="21" t="s">
+      <c r="W8" s="9">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="21" t="s">
+      <c r="AA8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE8" s="4" t="s">
@@ -2832,31 +2845,31 @@
       <c r="S9" s="6"/>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
-      <c r="V9" s="21" t="s">
+      <c r="V9" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W9" s="21">
-        <v>0</v>
-      </c>
-      <c r="X9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="21" t="s">
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="21" t="s">
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE9" s="4" t="s">
@@ -2927,31 +2940,31 @@
       <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="V10" s="21" t="s">
+      <c r="V10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="W10" s="21">
-        <v>0</v>
-      </c>
-      <c r="X10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="21" t="s">
+      <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="21" t="s">
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE10" s="4" t="s">
@@ -3037,28 +3050,28 @@
       <c r="V11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="W11" s="21">
-        <v>0</v>
-      </c>
-      <c r="X11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="21" t="s">
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="21" t="s">
+      <c r="AA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE11" s="4" t="s">
@@ -3151,25 +3164,25 @@
       <c r="W12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="X12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="21" t="s">
+      <c r="X12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="21" t="s">
+      <c r="AA12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE12" s="4" t="s">
@@ -3270,19 +3283,19 @@
       <c r="Y13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Z13" s="21" t="s">
+      <c r="Z13" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AA13" s="21">
+      <c r="AA13" s="9">
         <v>0</v>
       </c>
       <c r="AB13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AC13" s="21">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="21" t="s">
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE13" s="4" t="s">
@@ -3368,7 +3381,7 @@
       <c r="Z14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AA14" s="21">
+      <c r="AA14" s="9">
         <v>0</v>
       </c>
       <c r="AB14" s="4" t="s">
@@ -3377,7 +3390,7 @@
       <c r="AC14" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AD14" s="21" t="s">
+      <c r="AD14" s="9" t="s">
         <v>106</v>
       </c>
       <c r="AE14" s="4" t="s">
@@ -3880,4 +3893,353 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF32CB3-816D-41C2-A630-51D1A2B2367E}">
+  <dimension ref="B2:H21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="2"/>
+      <c r="C3" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="2">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="2">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="2">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="2">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="2">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="2">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="2">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C3:E3"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/report/Cycle-by-Cycle.xlsx
+++ b/report/Cycle-by-Cycle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314B8789-74DE-4E26-8180-200C284B8956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218D268A-F528-42F3-97BB-521545B8FA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="121">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -513,13 +513,20 @@
   <si>
     <t>R20</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Output Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,6 +544,19 @@
     <font>
       <b/>
       <sz val="7"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -668,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -732,6 +752,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2934,11 +2990,11 @@
       <c r="S10" s="6">
         <v>0</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0</v>
+      <c r="T10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="V10" s="9" t="s">
         <v>106</v>
@@ -3044,8 +3100,8 @@
       <c r="T11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="U11" s="3">
-        <v>0</v>
+      <c r="U11" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="V11" s="4" t="s">
         <v>9</v>
@@ -3897,347 +3953,437 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF32CB3-816D-41C2-A630-51D1A2B2367E}">
-  <dimension ref="B2:H21"/>
+  <dimension ref="B2:K21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="11" width="4.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="2"/>
-      <c r="C3" s="14" t="s">
+    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="25" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="5">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="I4" s="33">
+        <v>0</v>
+      </c>
+      <c r="J4" s="33">
+        <v>1</v>
+      </c>
+      <c r="K4" s="33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="26">
+        <v>0</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="5">
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+    </row>
+    <row r="6" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="26">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="5">
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+    </row>
+    <row r="7" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="26">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+    </row>
+    <row r="8" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="24">
+        <v>0</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="2">
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+    </row>
+    <row r="9" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="24">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="2">
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24">
         <v>2</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="2">
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="24">
         <v>3</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="2">
+      <c r="G11" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="33"/>
+    </row>
+    <row r="12" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="24">
         <v>4</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2">
+      <c r="H12" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="24">
         <v>5</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2">
+      <c r="I13" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="33"/>
+    </row>
+    <row r="14" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="24">
         <v>6</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="25" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="15" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="2">
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+    </row>
+    <row r="15" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="24">
         <v>7</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="25" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="2">
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+    </row>
+    <row r="16" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="24">
         <v>8</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="25" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="2">
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+    </row>
+    <row r="17" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="24">
         <v>9</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="2">
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="24">
         <v>10</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H18" s="25" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="2">
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+    </row>
+    <row r="19" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="24">
         <v>11</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3" t="s">
+      <c r="F19" s="25"/>
+      <c r="G19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="2">
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+    </row>
+    <row r="20" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="24">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3" t="s">
+      <c r="F20" s="25"/>
+      <c r="G20" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="H20" s="25" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+    </row>
+    <row r="21" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I3:K3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report/Cycle-by-Cycle.xlsx
+++ b/report/Cycle-by-Cycle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218D268A-F528-42F3-97BB-521545B8FA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B47EF7-FCF5-4C46-81B3-D7CF95F40644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="121">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -624,7 +624,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -684,11 +684,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -775,19 +795,16 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3953,14 +3970,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF32CB3-816D-41C2-A630-51D1A2B2367E}">
-  <dimension ref="B2:K21"/>
+  <dimension ref="B2:M21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="11" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="23" t="s">
         <v>120</v>
       </c>
@@ -3974,13 +3991,15 @@
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="29"/>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
-    </row>
-    <row r="4" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+    </row>
+    <row r="4" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="24" t="s">
         <v>0</v>
       </c>
@@ -4002,17 +4021,23 @@
       <c r="H4" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="33">
-        <v>0</v>
-      </c>
-      <c r="J4" s="33">
+      <c r="I4" s="30">
+        <v>0</v>
+      </c>
+      <c r="J4" s="30">
         <v>1</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="30">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="30">
+        <v>3</v>
+      </c>
+      <c r="M4" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B5" s="26">
         <v>0</v>
       </c>
@@ -4028,11 +4053,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
       <c r="H5" s="26"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-    </row>
-    <row r="6" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+    </row>
+    <row r="6" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="26">
         <v>1</v>
       </c>
@@ -4048,11 +4075,13 @@
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-    </row>
-    <row r="7" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+    </row>
+    <row r="7" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="26">
         <v>2</v>
       </c>
@@ -4068,11 +4097,13 @@
       <c r="F7" s="26"/>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-    </row>
-    <row r="8" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+    </row>
+    <row r="8" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="24">
         <v>0</v>
       </c>
@@ -4088,11 +4119,13 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="25"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-    </row>
-    <row r="9" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+    </row>
+    <row r="9" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="24">
         <v>1</v>
       </c>
@@ -4110,11 +4143,13 @@
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="25"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-    </row>
-    <row r="10" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+    </row>
+    <row r="10" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="24">
         <v>2</v>
       </c>
@@ -4132,13 +4167,15 @@
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="25"/>
-      <c r="I10" s="33" t="s">
+      <c r="I10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+    </row>
+    <row r="11" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="24">
         <v>3</v>
       </c>
@@ -4148,21 +4185,23 @@
       <c r="F11" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="34" t="s">
+      <c r="G11" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="34" t="s">
+      <c r="H11" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="I11" s="33" t="s">
+      <c r="I11" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="33" t="s">
+      <c r="J11" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="33"/>
-    </row>
-    <row r="12" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="24">
         <v>4</v>
       </c>
@@ -4181,24 +4220,30 @@
       <c r="G12" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H12" s="34" t="s">
+      <c r="H12" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="I12" s="33" t="s">
+      <c r="I12" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="33" t="s">
+      <c r="J12" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="33" t="s">
+      <c r="K12" s="30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L12" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="M12" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B13" s="24">
         <v>5</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="31" t="s">
         <v>116</v>
       </c>
       <c r="D13" s="25" t="s">
@@ -4216,22 +4261,26 @@
       <c r="H13" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="J13" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" s="33"/>
-    </row>
-    <row r="14" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+    </row>
+    <row r="14" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="24">
         <v>6</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="31" t="s">
         <v>117</v>
       </c>
       <c r="E14" s="25" t="s">
@@ -4246,11 +4295,15 @@
       <c r="H14" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-    </row>
-    <row r="15" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I14" s="30"/>
+      <c r="J14" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+    </row>
+    <row r="15" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="24">
         <v>7</v>
       </c>
@@ -4264,11 +4317,13 @@
       <c r="H15" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-    </row>
-    <row r="16" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+    </row>
+    <row r="16" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="24">
         <v>8</v>
       </c>
@@ -4284,11 +4339,13 @@
       <c r="H16" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-    </row>
-    <row r="17" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+    </row>
+    <row r="17" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="24">
         <v>9</v>
       </c>
@@ -4300,11 +4357,15 @@
       </c>
       <c r="G17" s="25"/>
       <c r="H17" s="25"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-    </row>
-    <row r="18" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="24">
         <v>10</v>
       </c>
@@ -4326,11 +4387,17 @@
       <c r="H18" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-    </row>
-    <row r="19" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I18" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+    </row>
+    <row r="19" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="24">
         <v>11</v>
       </c>
@@ -4350,11 +4417,19 @@
       <c r="H19" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-    </row>
-    <row r="20" spans="2:11" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I19" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+    </row>
+    <row r="20" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="24">
         <v>12</v>
       </c>
@@ -4374,16 +4449,24 @@
       <c r="H20" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-    </row>
-    <row r="21" spans="2:11" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="I20" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+    </row>
+    <row r="21" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I3:M3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report/Cycle-by-Cycle.xlsx
+++ b/report/Cycle-by-Cycle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harry\Desktop\Project\DSP-IN-VLSI-Final\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B47EF7-FCF5-4C46-81B3-D7CF95F40644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B81F05-B47B-4EB9-9541-9E2178B84A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="121">
   <si>
     <t>Cycle</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -562,7 +562,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,8 +623,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -684,31 +690,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -738,6 +724,48 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -745,6 +773,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -762,49 +799,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -815,11 +813,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFE6E7F4"/>
       <color rgb="FFFF5353"/>
       <color rgb="FFFFFFCD"/>
-      <color rgb="FFE6E7F4"/>
       <color rgb="FFCCECFF"/>
-      <color rgb="FFFFFF99"/>
       <color rgb="FFCCCCFF"/>
     </mruColors>
   </colors>
@@ -1122,45 +1120,45 @@
     <row r="1" spans="2:29" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="11" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="19" t="s">
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="11" t="s">
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="13"/>
-      <c r="AA2" s="11" t="s">
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="13"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="27"/>
     </row>
     <row r="3" spans="2:29" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -2262,60 +2260,60 @@
     <row r="1" spans="2:42" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="2"/>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="11" t="s">
+      <c r="D2" s="32"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17" t="s">
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="19" t="s">
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="11" t="s">
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="13"/>
-      <c r="AE2" s="11" t="s">
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+      <c r="AA2" s="26"/>
+      <c r="AB2" s="26"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="12"/>
-      <c r="AJ2" s="12"/>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="12"/>
-      <c r="AM2" s="13"/>
-      <c r="AN2" s="14" t="s">
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
+      <c r="AH2" s="26"/>
+      <c r="AI2" s="26"/>
+      <c r="AJ2" s="26"/>
+      <c r="AK2" s="26"/>
+      <c r="AL2" s="26"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="16"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="33"/>
     </row>
     <row r="3" spans="2:42" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
@@ -3970,503 +3968,1074 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF32CB3-816D-41C2-A630-51D1A2B2367E}">
-  <dimension ref="B2:M21"/>
+  <dimension ref="B2:V23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="13" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="6.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="5.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="23" t="s">
+    <row r="2" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28" t="s">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="32" t="s">
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-    </row>
-    <row r="4" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="25" t="s">
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="24"/>
+    </row>
+    <row r="4" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="30">
-        <v>0</v>
-      </c>
-      <c r="J4" s="30">
+      <c r="I4" s="15">
+        <v>0</v>
+      </c>
+      <c r="J4" s="15">
         <v>1</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="15">
         <v>2</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="15">
         <v>3</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="15">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="26">
-        <v>0</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="N4" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="P4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="V4" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="37">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-    </row>
-    <row r="6" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="26">
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O5" s="13">
+        <v>0</v>
+      </c>
+      <c r="P5" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>0</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S5" s="13">
+        <v>0</v>
+      </c>
+      <c r="T5" s="13">
+        <v>0</v>
+      </c>
+      <c r="U5" s="13">
+        <v>0</v>
+      </c>
+      <c r="V5" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="37">
         <v>1</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-    </row>
-    <row r="7" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="26">
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O6" s="13">
+        <v>0</v>
+      </c>
+      <c r="P6" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>0</v>
+      </c>
+      <c r="R6" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S6" s="13">
+        <v>0</v>
+      </c>
+      <c r="T6" s="13">
+        <v>0</v>
+      </c>
+      <c r="U6" s="13">
+        <v>0</v>
+      </c>
+      <c r="V6" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="37">
         <v>2</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-    </row>
-    <row r="8" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="24">
-        <v>0</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O7" s="13">
+        <v>0</v>
+      </c>
+      <c r="P7" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S7" s="13">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13">
+        <v>0</v>
+      </c>
+      <c r="U7" s="13">
+        <v>0</v>
+      </c>
+      <c r="V7" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="12">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-    </row>
-    <row r="9" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="24">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" s="13">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>0</v>
+      </c>
+      <c r="R8" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S8" s="13">
+        <v>0</v>
+      </c>
+      <c r="T8" s="13">
+        <v>0</v>
+      </c>
+      <c r="U8" s="13">
+        <v>0</v>
+      </c>
+      <c r="V8" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="12">
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O9" s="13">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S9" s="13">
+        <v>0</v>
+      </c>
+      <c r="T9" s="13">
+        <v>0</v>
+      </c>
+      <c r="U9" s="13">
+        <v>0</v>
+      </c>
+      <c r="V9" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="12">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-    </row>
-    <row r="10" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="24">
-        <v>2</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O10" s="13">
+        <v>0</v>
+      </c>
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>0</v>
+      </c>
+      <c r="R10" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S10" s="13">
+        <v>0</v>
+      </c>
+      <c r="T10" s="13">
+        <v>0</v>
+      </c>
+      <c r="U10" s="13">
+        <v>0</v>
+      </c>
+      <c r="V10" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="12">
+        <v>3</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O11" s="13">
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S11" s="13">
+        <v>0</v>
+      </c>
+      <c r="T11" s="13">
+        <v>0</v>
+      </c>
+      <c r="U11" s="13">
+        <v>0</v>
+      </c>
+      <c r="V11" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="12">
+        <v>4</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="O12" s="13">
+        <v>0</v>
+      </c>
+      <c r="P12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>0</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S12" s="13">
+        <v>0</v>
+      </c>
+      <c r="T12" s="13">
+        <v>0</v>
+      </c>
+      <c r="U12" s="13">
+        <v>0</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="12">
+        <v>5</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="13">
+        <v>0</v>
+      </c>
+      <c r="P13" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S13" s="13">
+        <v>0</v>
+      </c>
+      <c r="T13" s="13">
+        <v>0</v>
+      </c>
+      <c r="U13" s="13">
+        <v>0</v>
+      </c>
+      <c r="V13" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="12">
+        <v>6</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>0</v>
+      </c>
+      <c r="R14" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S14" s="13">
+        <v>0</v>
+      </c>
+      <c r="T14" s="13">
+        <v>0</v>
+      </c>
+      <c r="U14" s="13">
+        <v>0</v>
+      </c>
+      <c r="V14" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="12">
+        <v>7</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="G15" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="M15" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R15" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="S15" s="13">
+        <v>0</v>
+      </c>
+      <c r="T15" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U15" s="13">
+        <v>0</v>
+      </c>
+      <c r="V15" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="12">
+        <v>8</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S16" s="13">
+        <v>0</v>
+      </c>
+      <c r="T16" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="12">
+        <v>9</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="H17" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="24">
-        <v>3</v>
-      </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="I11" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-    </row>
-    <row r="12" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="24">
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="12">
+        <v>10</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="25" t="s">
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>116</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="24">
+      <c r="O18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V18" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="12">
+        <v>11</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R19" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U19" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V19" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="12">
+        <v>12</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="25" t="s">
+      <c r="E20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-    </row>
-    <row r="14" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="24">
-        <v>6</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="25" t="s">
+      <c r="P20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="Q20" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="R20" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="30"/>
-      <c r="J14" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="K14" s="30"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-    </row>
-    <row r="15" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="24">
+      <c r="U20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V20" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="12">
+        <v>13</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25" t="s">
+      <c r="D21" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R21" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="S21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T21" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-    </row>
-    <row r="16" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="24">
+      <c r="V21" s="13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="12">
+        <v>14</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25" t="s">
+      <c r="D22" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="J22" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="R22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="S22" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="25" t="s">
+      <c r="T22" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="V22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-    </row>
-    <row r="17" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="24">
-        <v>9</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-    </row>
-    <row r="18" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="24">
-        <v>10</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-    </row>
-    <row r="19" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="24">
-        <v>11</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="K19" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-    </row>
-    <row r="20" spans="2:13" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="24">
-        <v>12</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="K20" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-    </row>
-    <row r="21" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    </row>
+    <row r="23" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:V3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
